--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T16:19:33+00:00</t>
+    <t>2026-06-15T16:22:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T16:22:03+00:00</t>
+    <t>2026-06-22T07:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T07:18:24+00:00</t>
+    <t>2026-07-23T09:21:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -350,7 +350,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260619134042</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:21:02+00:00</t>
+    <t>2026-07-23T09:32:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -347,7 +347,7 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>required</t>
+    <t>example</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260619134042</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:32:23+00:00</t>
+    <t>2026-07-23T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:36:51+00:00</t>
+    <t>2026-07-23T09:46:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:46:12+00:00</t>
+    <t>2026-07-23T09:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T09:54:31+00:00</t>
+    <t>2026-07-23T10:00:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T10:00:41+00:00</t>
+    <t>2026-07-31T09:43:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-method-extension.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T09:43:50+00:00</t>
+    <t>2026-07-31T14:55:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
